--- a/fase1/6_2_table.xlsx
+++ b/fase1/6_2_table.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rjorg\Desktop\Universidade\Universidade de Coimbra\Introducao_a_Aprendizagem_Computacional\projeto\IML_project_app\app\fase1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neves/Desktop/mestrado/IAC/projeto/IAC_project/fase1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBCDC671-489A-4610-A759-BBFF909C43A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB706CE-02E1-CB4E-A2F2-B57ECF899139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10344" yWindow="0" windowWidth="12792" windowHeight="12336" xr2:uid="{48E65019-C06B-45E5-81BB-A7844360E2A9}"/>
+    <workbookView xWindow="10880" yWindow="-19580" windowWidth="20000" windowHeight="15500" xr2:uid="{48E65019-C06B-45E5-81BB-A7844360E2A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="18">
   <si>
     <t>Group Member</t>
   </si>
@@ -90,6 +89,9 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>João Neves</t>
   </si>
 </sst>
 </file>
@@ -462,16 +464,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4255A9F0-7BF3-41E5-A665-DB57A46F4CFA}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="12" max="12" width="17.5546875" customWidth="1"/>
+    <col min="12" max="12" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -512,7 +514,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -553,7 +555,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -594,7 +596,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -635,7 +637,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -676,7 +678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -717,7 +719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -758,7 +760,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -799,7 +801,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -840,7 +842,336 @@
         <v>16</v>
       </c>
     </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="L10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="H11" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="L11" t="s">
+        <v>5</v>
+      </c>
+      <c r="M11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="E12" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="L12" t="s">
+        <v>6</v>
+      </c>
+      <c r="M12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
+        <v>6</v>
+      </c>
+      <c r="M13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="L14" t="s">
+        <v>7</v>
+      </c>
+      <c r="M14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.54</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="L15" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" t="s">
+        <v>9</v>
+      </c>
+      <c r="M16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="L17" t="s">
+        <v>7</v>
+      </c>
+      <c r="M17" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>